--- a/output/pdf_financials_xlsx/ANDC.xlsx
+++ b/output/pdf_financials_xlsx/ANDC.xlsx
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>1.81056</v>
+        <v>3.400866</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5.540485</v>
+        <v>8.999636000000001</v>
       </c>
     </row>
     <row r="93">
@@ -2572,7 +2572,11 @@
           <t>Warrant reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>1.590306</v>
       </c>

--- a/output/pdf_financials_xlsx/ANDC.xlsx
+++ b/output/pdf_financials_xlsx/ANDC.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.040701</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.031506</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.162595</v>
+        <v>-1.203296</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.600077</v>
+        <v>-5.631583</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.148357</v>
+        <v>-1.189058</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.565139</v>
+        <v>-5.596645</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.291871</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.357088</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.291871</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.357088</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.6288550000000001</v>
+        <v>0.336984</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.765235</v>
+        <v>0.408147</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">

--- a/output/pdf_financials_xlsx/ANDC.xlsx
+++ b/output/pdf_financials_xlsx/ANDC.xlsx
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.10461</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.017502</v>
       </c>
     </row>
     <row r="68">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.111295</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.111295</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.609151</v>
+        <v>-0.720446</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-2.269473</v>
@@ -3068,7 +3068,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>-0.111295</v>
       </c>
